--- a/AAII_Financials/Yearly/ISUZY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ISUZY_YR_FIN.xlsx
@@ -302,7 +302,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -344,7 +344,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Yearly/ISUZY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ISUZY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="92">
   <si>
     <t>ISUZY</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -653,135 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21423200</v>
+      </c>
+      <c r="E8" s="3">
         <v>22390500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24038500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20705000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17252900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19329900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19395100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19494000</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>17282600</v>
+      </c>
+      <c r="E9" s="3">
         <v>17893200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19561200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16931900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14512900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16081100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15930600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16013600</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4140600</v>
+      </c>
+      <c r="E10" s="3">
         <v>4497300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4477300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3773100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2740000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3248800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3464500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3480400</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,35 +808,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3">
         <v>819100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>894400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>862200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>822800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>910800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>892500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>911400</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,63 +865,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E14" s="3">
         <v>60500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>36000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>160300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>77800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>35200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-23300</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E15" s="3">
         <v>145400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>156700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>176500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>110400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>111200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>103800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>88900</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -911,62 +939,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>19893200</v>
+      </c>
+      <c r="E17" s="3">
         <v>20452800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22131200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19163400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16387300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18023400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17799700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17923800</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1530000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1937700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1907300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1541600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>865600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1306500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1595400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1570200</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -978,143 +1013,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-48200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-65000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-63000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-123700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-56300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-61300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-71700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-28200</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1735500</v>
+      </c>
+      <c r="E21" s="3">
         <v>2148100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2127000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1841700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1032300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1479100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1770900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1687300</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E22" s="3">
         <v>27700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>26300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>19600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17800</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1603500</v>
+      </c>
+      <c r="E23" s="3">
         <v>2020400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2029900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1682200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>785100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1333700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1679500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1658000</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>437300</v>
+      </c>
+      <c r="E24" s="3">
         <v>556900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>551000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>391700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>310100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>381200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>433500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>461900</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1139,63 +1190,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1166200</v>
+      </c>
+      <c r="E26" s="3">
         <v>1463500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1478900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1290600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>475000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>952500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1246000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1196200</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>897300</v>
+      </c>
+      <c r="E27" s="3">
         <v>1166500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1141500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1039200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>386100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>754900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1023800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>994900</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1220,9 +1280,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1247,9 +1310,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1274,9 +1340,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1301,63 +1370,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E32" s="3">
         <v>65000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>63000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>123700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>56300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>61300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>71700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>28200</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>897300</v>
+      </c>
+      <c r="E33" s="3">
         <v>1166500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1141500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1039200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>386200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>754900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1023800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>994900</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1382,68 +1460,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>897300</v>
+      </c>
+      <c r="E35" s="3">
         <v>1166500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1141500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1039200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>386200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>754900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1023800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>994900</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1455,8 +1542,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1468,40 +1556,44 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>2433400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2649700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2885500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2931800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3659700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2987200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2961100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3265600</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>149900</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1521,198 +1613,222 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>4424700</v>
+      </c>
+      <c r="E43" s="3">
         <v>4238600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4484200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4616100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3820400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3742200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3762300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3588800</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>4529800</v>
+      </c>
+      <c r="E44" s="3">
         <v>4441200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4614700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3933600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2606400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3009300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2775200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2599500</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E45" s="3">
         <v>687100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>820800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>794600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>613000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>665700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>541900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>555000</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>12289800</v>
+      </c>
+      <c r="E46" s="3">
         <v>12016600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12805300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12276200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10699400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10404400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10040300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10311800</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>1833600</v>
+      </c>
+      <c r="E47" s="3">
         <v>2213800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2039800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2495000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2081400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1745900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1856200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2033900</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>6379100</v>
+      </c>
+      <c r="E48" s="3">
         <v>6450700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7038600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7566900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6940100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7080900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6600000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6646100</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>701700</v>
+      </c>
+      <c r="E49" s="3">
         <v>592300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>561800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>719800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>171500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>216300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>229000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>251500</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1737,9 +1853,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1764,14 +1883,17 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>375100</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -1791,9 +1913,12 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1818,36 +1943,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>21963200</v>
+      </c>
+      <c r="E54" s="3">
         <v>21572800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22919500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23520100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20298300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20000500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19230200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19467300</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1859,8 +1990,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1872,170 +2004,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>3258000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3650300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4240400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4090300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3507500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3363700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3494600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3577900</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1798300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1412000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>944000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1217300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>531900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>796900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>677900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>726300</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1250100</v>
+      </c>
+      <c r="E59" s="3">
         <v>966500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1028100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1063500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>893300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>803200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>816200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>839000</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>7411700</v>
+      </c>
+      <c r="E60" s="3">
         <v>7161000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7288100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7396600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5641700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5605800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5652300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5834300</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>2715500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2269400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2916100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3151200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2330300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2332300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2005900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1906400</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>308200</v>
+      </c>
+      <c r="E62" s="3">
         <v>315600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>297200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>307200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>239900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>209700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>211700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>154000</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2060,9 +2211,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2087,9 +2241,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2114,36 +2271,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>11235800</v>
+      </c>
+      <c r="E66" s="3">
         <v>10604400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11558700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12037100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9403000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9467400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9155900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9237000</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2155,8 +2318,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2181,9 +2345,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2208,9 +2375,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,9 +2405,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2262,36 +2435,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>7117000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7485400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7686300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7645100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7682500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8594000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7867900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7392300</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2316,9 +2495,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2343,9 +2525,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2370,36 +2555,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>9635000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9657200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9843300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9833300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9238600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8856100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8390800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8658600</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2424,68 +2615,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>897300</v>
+      </c>
+      <c r="E81" s="3">
         <v>1166500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1141500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1039200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>386200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>754900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1023800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>994900</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2497,35 +2697,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>737200</v>
+      </c>
+      <c r="E83" s="3">
         <v>760500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>806800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>809800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>744600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>708300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>631500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>624400</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2550,9 +2754,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2577,9 +2784,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2604,9 +2814,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2631,9 +2844,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2658,36 +2874,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1453500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1973900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1708300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1416900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2015600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1149600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1412700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1664700</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2699,35 +2921,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1167900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1066900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-807300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-826200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-885100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-961600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-855200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-936300</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2752,9 +2978,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2779,36 +3008,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1187900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1025300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-605800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3465800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-844600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-861100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-781200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1007800</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2820,13 +3055,14 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>473400</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -2846,9 +3082,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2873,9 +3112,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2900,9 +3142,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2927,88 +3172,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-431300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-958500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1056000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1532900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-499800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-233800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-964800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-41700</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E101" s="3">
         <v>168200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>136300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>145800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>76500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-67100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>43500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>37000</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-94400</v>
+      </c>
+      <c r="E102" s="3">
         <v>158300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>182800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-370200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>747700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-289900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>652200</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ISUZY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ISUZY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
   <si>
     <t>ISUZY</t>
   </si>
@@ -295,9 +295,6 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -711,7 +708,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21423200</v>
+        <v>21607300</v>
       </c>
       <c r="E8" s="3">
         <v>22390500</v>
@@ -741,7 +738,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>17282600</v>
+        <v>17184500</v>
       </c>
       <c r="E9" s="3">
         <v>17893200</v>
@@ -771,7 +768,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4140600</v>
+        <v>4422800</v>
       </c>
       <c r="E10" s="3">
         <v>4497300</v>
@@ -814,8 +811,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
+      <c r="D12" s="3">
+        <v>914900</v>
       </c>
       <c r="E12" s="3">
         <v>819100</v>
@@ -875,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>62700</v>
+        <v>25500</v>
       </c>
       <c r="E14" s="3">
         <v>60500</v>
@@ -905,7 +902,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>157300</v>
+        <v>1009700</v>
       </c>
       <c r="E15" s="3">
         <v>145400</v>
@@ -946,7 +943,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>19893200</v>
+        <v>20049500</v>
       </c>
       <c r="E17" s="3">
         <v>20452800</v>
@@ -976,7 +973,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1530000</v>
+        <v>1557800</v>
       </c>
       <c r="E18" s="3">
         <v>1937700</v>
@@ -1020,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-48200</v>
+        <v>-21100</v>
       </c>
       <c r="E20" s="3">
         <v>-65000</v>
@@ -1050,7 +1047,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1735500</v>
+        <v>2588600</v>
       </c>
       <c r="E21" s="3">
         <v>2148100</v>
@@ -1080,7 +1077,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>33300</v>
+        <v>38400</v>
       </c>
       <c r="E22" s="3">
         <v>27700</v>
@@ -1110,7 +1107,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1603500</v>
+        <v>1635800</v>
       </c>
       <c r="E23" s="3">
         <v>2020400</v>
@@ -1140,7 +1137,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>437300</v>
+        <v>427700</v>
       </c>
       <c r="E24" s="3">
         <v>556900</v>
@@ -1200,7 +1197,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1166200</v>
+        <v>1208200</v>
       </c>
       <c r="E26" s="3">
         <v>1463500</v>
@@ -1230,7 +1227,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>897300</v>
+        <v>935300</v>
       </c>
       <c r="E27" s="3">
         <v>1166500</v>
@@ -1380,7 +1377,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>48200</v>
+        <v>21100</v>
       </c>
       <c r="E32" s="3">
         <v>65000</v>
@@ -1410,7 +1407,7 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>897300</v>
+        <v>935300</v>
       </c>
       <c r="E33" s="3">
         <v>1166500</v>
@@ -1470,7 +1467,7 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>897300</v>
+        <v>935300</v>
       </c>
       <c r="E35" s="3">
         <v>1166500</v>
@@ -1563,7 +1560,7 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>2433400</v>
+        <v>2395400</v>
       </c>
       <c r="E41" s="3">
         <v>2649700</v>
@@ -1593,7 +1590,7 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>149900</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1623,7 +1620,7 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>4424700</v>
+        <v>4464100</v>
       </c>
       <c r="E43" s="3">
         <v>4238600</v>
@@ -1653,7 +1650,7 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>4529800</v>
+        <v>4553000</v>
       </c>
       <c r="E44" s="3">
         <v>4441200</v>
@@ -1683,7 +1680,7 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>752000</v>
+        <v>710200</v>
       </c>
       <c r="E45" s="3">
         <v>687100</v>
@@ -1713,7 +1710,7 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>12289800</v>
+        <v>12122700</v>
       </c>
       <c r="E46" s="3">
         <v>12016600</v>
@@ -1743,7 +1740,7 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>1833600</v>
+        <v>2310200</v>
       </c>
       <c r="E47" s="3">
         <v>2213800</v>
@@ -1773,7 +1770,7 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>6379100</v>
+        <v>6326800</v>
       </c>
       <c r="E48" s="3">
         <v>6450700</v>
@@ -1803,7 +1800,7 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>701700</v>
+        <v>992400</v>
       </c>
       <c r="E49" s="3">
         <v>592300</v>
@@ -1893,7 +1890,7 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>375100</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -1953,7 +1950,7 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>21963200</v>
+        <v>22059100</v>
       </c>
       <c r="E54" s="3">
         <v>21572800</v>
@@ -2011,7 +2008,7 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>3258000</v>
+        <v>4568000</v>
       </c>
       <c r="E57" s="3">
         <v>3650300</v>
@@ -2041,7 +2038,7 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>1798300</v>
+        <v>1916000</v>
       </c>
       <c r="E58" s="3">
         <v>1412000</v>
@@ -2071,7 +2068,7 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1250100</v>
+        <v>1101500</v>
       </c>
       <c r="E59" s="3">
         <v>966500</v>
@@ -2101,7 +2098,7 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>7411700</v>
+        <v>7585600</v>
       </c>
       <c r="E60" s="3">
         <v>7161000</v>
@@ -2131,7 +2128,7 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>2715500</v>
+        <v>3151400</v>
       </c>
       <c r="E61" s="3">
         <v>2269400</v>
@@ -2161,7 +2158,7 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>308200</v>
+        <v>403400</v>
       </c>
       <c r="E62" s="3">
         <v>315600</v>
@@ -2281,7 +2278,7 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>11235800</v>
+        <v>11790800</v>
       </c>
       <c r="E66" s="3">
         <v>10604400</v>
@@ -2445,7 +2442,7 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>7117000</v>
+        <v>7762400</v>
       </c>
       <c r="E72" s="3">
         <v>7485400</v>
@@ -2565,7 +2562,7 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>9635000</v>
+        <v>9167800</v>
       </c>
       <c r="E76" s="3">
         <v>9657200</v>
@@ -2660,7 +2657,7 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>897300</v>
+        <v>935300</v>
       </c>
       <c r="E81" s="3">
         <v>1166500</v>
@@ -2704,7 +2701,7 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>737200</v>
+        <v>1009700</v>
       </c>
       <c r="E83" s="3">
         <v>760500</v>
@@ -2884,7 +2881,7 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>1453500</v>
+        <v>1696600</v>
       </c>
       <c r="E89" s="3">
         <v>1973900</v>
@@ -2928,7 +2925,7 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-1167900</v>
+        <v>-1060600</v>
       </c>
       <c r="E91" s="3">
         <v>-1066900</v>
@@ -3018,7 +3015,7 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-1187900</v>
+        <v>-1351200</v>
       </c>
       <c r="E94" s="3">
         <v>-1025300</v>
@@ -3062,7 +3059,7 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>473400</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -3182,7 +3179,7 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-431300</v>
+        <v>-605000</v>
       </c>
       <c r="E100" s="3">
         <v>-958500</v>
@@ -3212,7 +3209,7 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>71400</v>
+        <v>55900</v>
       </c>
       <c r="E101" s="3">
         <v>168200</v>
@@ -3242,7 +3239,7 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-94400</v>
+        <v>-203800</v>
       </c>
       <c r="E102" s="3">
         <v>158300</v>
